--- a/_arch/Feat_Import.xlsx
+++ b/_arch/Feat_Import.xlsx
@@ -5,18 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dean/Documents/source/OMS/Strategy.EXP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dean/Documents/source/ML_Trading/_arch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52AE446-7E41-A040-81EE-12438F026D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6A3588-A16C-A948-80BE-4EB609F8AF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9600" yWindow="2140" windowWidth="28040" windowHeight="16240" activeTab="2" xr2:uid="{05A42074-7068-8940-8818-09045A99FC51}"/>
+    <workbookView xWindow="7760" yWindow="2260" windowWidth="28040" windowHeight="16240" activeTab="1" xr2:uid="{05A42074-7068-8940-8818-09045A99FC51}"/>
   </bookViews>
   <sheets>
-    <sheet name="IND_F" sheetId="1" r:id="rId1"/>
-    <sheet name="Refried" sheetId="4" r:id="rId2"/>
-    <sheet name="LUCKY_F" sheetId="2" r:id="rId3"/>
-    <sheet name="IND_LSTM" sheetId="3" r:id="rId4"/>
+    <sheet name="Lucky13" sheetId="5" r:id="rId1"/>
+    <sheet name="Sheet4" sheetId="8" r:id="rId2"/>
+    <sheet name="IND_F" sheetId="1" r:id="rId3"/>
+    <sheet name="Refried" sheetId="4" r:id="rId4"/>
+    <sheet name="LUCKY_F" sheetId="2" r:id="rId5"/>
+    <sheet name="IND_LSTM" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="237">
   <si>
     <t>SDKC7</t>
   </si>
@@ -681,13 +683,214 @@
   </si>
   <si>
     <t>STOK1565seq4</t>
+  </si>
+  <si>
+    <r>
+      <t>'RSI'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'SDBB91'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'SDLR310'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'ROC'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'SDKC91'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'ATR33'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'ATR32'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'SDKC9'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'STOK1'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'ATR2'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'ATR21'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'ATR3'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <t>'ATR31'</t>
+  </si>
+  <si>
+    <t>ATR31</t>
+  </si>
+  <si>
+    <t>ATR34</t>
+  </si>
+  <si>
+    <t>Feat</t>
+  </si>
+  <si>
+    <t>#Uses</t>
+  </si>
+  <si>
+    <t>Uses</t>
+  </si>
+  <si>
+    <t>Perm</t>
+  </si>
+  <si>
+    <t>Comp</t>
+  </si>
+  <si>
+    <t>Val</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Top 88%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -701,8 +904,20 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFCE9178"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -721,6 +936,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -734,60 +955,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1167,11 +1355,1720 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224462D2-154F-E14E-902D-7BB3C4C20791}">
-  <dimension ref="C1:S59"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A281859-746C-0D4B-B71C-635CE415EC7B}">
+  <dimension ref="B2:U46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" t="s">
+        <v>234</v>
+      </c>
+      <c r="N2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>232</v>
+      </c>
+      <c r="R2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3">
+        <v>0.68621671199798495</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3">
+        <v>0.163269653916358</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3">
+        <v>4</v>
+      </c>
+      <c r="T3">
+        <f>R3+O3</f>
+        <v>4</v>
+      </c>
+      <c r="U3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <v>5.6065507233142797E-2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4">
+        <v>0.153331443667411</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T15" si="0">R4+O4</f>
+        <v>5</v>
+      </c>
+      <c r="U4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5">
+        <v>5.3621955215930897E-2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5">
+        <v>0.14040680229663799</v>
+      </c>
+      <c r="N5" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R5">
+        <v>3</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="U5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6">
+        <v>5.2865281701087903E-2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>227</v>
+      </c>
+      <c r="H6">
+        <v>0.139873266220092</v>
+      </c>
+      <c r="N6" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="U6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7">
+        <v>5.2704039961099597E-2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7">
+        <v>0.13896705210208801</v>
+      </c>
+      <c r="N7" t="s">
+        <v>43</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="U7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8">
+        <v>5.11732250452041E-2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8">
+        <v>0.13720260560512501</v>
+      </c>
+      <c r="N8" t="s">
+        <v>227</v>
+      </c>
+      <c r="O8">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>227</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="U8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9">
+        <v>4.7353256493806797E-2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9">
+        <v>0.12694919109344399</v>
+      </c>
+      <c r="N9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>23</v>
+      </c>
+      <c r="R9">
+        <v>4</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="U9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="N10" t="s">
+        <v>37</v>
+      </c>
+      <c r="O10">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>37</v>
+      </c>
+      <c r="R10">
+        <v>3</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="U10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="N11" t="s">
+        <v>228</v>
+      </c>
+      <c r="O11">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>228</v>
+      </c>
+      <c r="R11">
+        <v>3</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U11" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="N12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12">
+        <v>3</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13">
+        <v>0.68621671199798495</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13">
+        <v>0.274377854413272</v>
+      </c>
+      <c r="I13">
+        <v>2.5939899393119998E-3</v>
+      </c>
+      <c r="N13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R13">
+        <v>4</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14">
+        <v>5.6065507233142797E-2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14">
+        <v>1.3039425855158901E-2</v>
+      </c>
+      <c r="I14">
+        <v>2.5588046498377201E-3</v>
+      </c>
+      <c r="N14" t="s">
+        <v>36</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>36</v>
+      </c>
+      <c r="R14">
+        <v>3</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="U14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15">
+        <v>5.3621955215930897E-2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15">
+        <v>1.30021437226209E-2</v>
+      </c>
+      <c r="I15">
+        <v>2.0318976005770902E-3</v>
+      </c>
+      <c r="N15" t="s">
+        <v>34</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16">
+        <v>5.2865281701087903E-2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16">
+        <v>1.2918258924410401E-2</v>
+      </c>
+      <c r="I16">
+        <v>2.5186833075297901E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C17">
+        <v>5.2704039961099597E-2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17">
+        <v>1.2843694659334499E-2</v>
+      </c>
+      <c r="I17">
+        <v>2.7434051591547202E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18">
+        <v>5.11732250452041E-2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>228</v>
+      </c>
+      <c r="H18">
+        <v>1.07558952372075E-2</v>
+      </c>
+      <c r="I18">
+        <v>1.6762454764743099E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19">
+        <v>4.7353256493806797E-2</v>
+      </c>
+      <c r="G19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19">
+        <v>8.1741075589523999E-3</v>
+      </c>
+      <c r="I19">
+        <v>2.17072395311857E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P20" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P21">
+        <v>7</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P22">
+        <v>7</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23">
+        <v>0.16493113338947199</v>
+      </c>
+      <c r="G23" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23">
+        <v>5.2356980930791204E-3</v>
+      </c>
+      <c r="I23">
+        <v>1.4300012603516701E-3</v>
+      </c>
+      <c r="P23">
+        <v>6</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24">
+        <v>0.15555378794670099</v>
+      </c>
+      <c r="G24" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24">
+        <v>4.9523269769302797E-3</v>
+      </c>
+      <c r="I24">
+        <v>1.75953449691788E-3</v>
+      </c>
+      <c r="P24">
+        <v>5</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25">
+        <v>0.14743372797966001</v>
+      </c>
+      <c r="G25" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25">
+        <v>4.2989065208694803E-3</v>
+      </c>
+      <c r="I25">
+        <v>1.0255485811918701E-3</v>
+      </c>
+      <c r="P25">
+        <v>5</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26">
+        <v>0.14161115884780801</v>
+      </c>
+      <c r="G26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26">
+        <v>3.8121749566609399E-3</v>
+      </c>
+      <c r="I26">
+        <v>7.1746159946730996E-4</v>
+      </c>
+      <c r="P26">
+        <v>5</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27">
+        <v>0.136847808957099</v>
+      </c>
+      <c r="G27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27">
+        <v>3.46712895052677E-3</v>
+      </c>
+      <c r="I27">
+        <v>1.0069995891738501E-3</v>
+      </c>
+      <c r="P27">
+        <v>5</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28">
+        <v>0.13288007676601399</v>
+      </c>
+      <c r="G28" t="s">
+        <v>37</v>
+      </c>
+      <c r="H28">
+        <v>3.3887851713562101E-3</v>
+      </c>
+      <c r="I28">
+        <v>1.0024933816547199E-3</v>
+      </c>
+      <c r="P28">
+        <v>4</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29">
+        <v>0.120742350816726</v>
+      </c>
+      <c r="G29" t="s">
+        <v>228</v>
+      </c>
+      <c r="H29">
+        <v>2.76870249366586E-3</v>
+      </c>
+      <c r="I29">
+        <v>7.9426688509214396E-4</v>
+      </c>
+      <c r="P29">
+        <v>4</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P30">
+        <v>4</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P31">
+        <v>4</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32">
+        <v>0.15691475570201799</v>
+      </c>
+      <c r="G32" t="s">
+        <v>38</v>
+      </c>
+      <c r="H32">
+        <v>5.4344338685774199E-3</v>
+      </c>
+      <c r="I32">
+        <v>1.3004927040534599E-3</v>
+      </c>
+      <c r="P32">
+        <v>3</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33">
+        <v>0.15644374489784199</v>
+      </c>
+      <c r="G33" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33">
+        <v>4.15718148900736E-3</v>
+      </c>
+      <c r="I33">
+        <v>1.5627594073341E-3</v>
+      </c>
+      <c r="P33">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>0.15058366954326599</v>
+      </c>
+      <c r="G34" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34">
+        <v>3.1274349533252799E-3</v>
+      </c>
+      <c r="I34">
+        <v>8.8233200987207602E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35">
+        <v>0.13505525887012401</v>
+      </c>
+      <c r="G35" t="s">
+        <v>228</v>
+      </c>
+      <c r="H35">
+        <v>2.4078346294287502E-3</v>
+      </c>
+      <c r="I35">
+        <v>1.1486112255410701E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36">
+        <v>0.13417842984199499</v>
+      </c>
+      <c r="G36" t="s">
+        <v>37</v>
+      </c>
+      <c r="H36">
+        <v>1.30016958733748E-3</v>
+      </c>
+      <c r="I36">
+        <v>1.430958152401E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37">
+        <v>0.13413907587528201</v>
+      </c>
+      <c r="G37" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37">
+        <v>7.9140757490105899E-4</v>
+      </c>
+      <c r="I37">
+        <v>1.27361040540877E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>227</v>
+      </c>
+      <c r="C38">
+        <v>0.13268508017063099</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40">
+        <v>0.44884106516838002</v>
+      </c>
+      <c r="G40" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40">
+        <v>0.13318008906196399</v>
+      </c>
+      <c r="I40">
+        <v>1.24686547348789E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41">
+        <v>0.115297175943851</v>
+      </c>
+      <c r="G41" t="s">
+        <v>38</v>
+      </c>
+      <c r="H41">
+        <v>0.115760722591811</v>
+      </c>
+      <c r="I41">
+        <v>1.64823390856078E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42">
+        <v>0.11411864310503</v>
+      </c>
+      <c r="G42" t="s">
+        <v>37</v>
+      </c>
+      <c r="H42">
+        <v>6.3044693241026101E-2</v>
+      </c>
+      <c r="I42">
+        <v>1.3379327846371101E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43">
+        <v>8.8290140032768194E-2</v>
+      </c>
+      <c r="G43" t="s">
+        <v>228</v>
+      </c>
+      <c r="H43">
+        <v>5.9318153136098901E-2</v>
+      </c>
+      <c r="I43">
+        <v>1.500415640978E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44">
+        <v>7.9414144158363301E-2</v>
+      </c>
+      <c r="G44" t="s">
+        <v>39</v>
+      </c>
+      <c r="H44">
+        <v>3.7901815493897199E-2</v>
+      </c>
+      <c r="I44">
+        <v>1.06326917252889E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45">
+        <v>7.8326664865016896E-2</v>
+      </c>
+      <c r="G45" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45">
+        <v>2.38880775956875E-2</v>
+      </c>
+      <c r="I45">
+        <v>9.3377723737378599E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46">
+        <v>7.5712136924266801E-2</v>
+      </c>
+      <c r="G46" t="s">
+        <v>36</v>
+      </c>
+      <c r="H46">
+        <v>1.9968629996213901E-2</v>
+      </c>
+      <c r="I46">
+        <v>9.7549300369407697E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="P21:Q33">
+    <sortCondition descending="1" ref="P21:P33"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9716CA3-06B7-C84A-8B30-704386DE312A}">
+  <dimension ref="B4:P39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" t="s">
+        <v>234</v>
+      </c>
+      <c r="K4" t="s">
+        <v>229</v>
+      </c>
+      <c r="L4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5">
+        <v>0.68621671199798495</v>
+      </c>
+      <c r="F5" t="s">
+        <v>229</v>
+      </c>
+      <c r="G5" t="s">
+        <v>235</v>
+      </c>
+      <c r="K5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5">
+        <v>0.163269653916358</v>
+      </c>
+      <c r="N5" t="s">
+        <v>229</v>
+      </c>
+      <c r="O5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>5.6065507233142797E-2</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.785747997462747</v>
+      </c>
+      <c r="H6" s="1">
+        <f>G6/$G$21</f>
+        <v>0.3571496005569389</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6">
+        <v>0.153331443667411</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" s="8">
+        <v>0.163269653916358</v>
+      </c>
+      <c r="P6" s="1">
+        <f>O6/$O$19</f>
+        <v>8.8573893476511331E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>5.3621955215930897E-2</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.44884106516838002</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" ref="H7:H18" si="0">G7/$G$21</f>
+        <v>8.9768213301206323E-2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>236</v>
+      </c>
+      <c r="K7" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7">
+        <v>0.14040680229663799</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O7" s="8">
+        <v>0.153331443667411</v>
+      </c>
+      <c r="P7" s="1">
+        <f t="shared" ref="P7:P16" si="1">O7/$O$19</f>
+        <v>8.3182407950435799E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8">
+        <v>5.2865281701087903E-2</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.40078902244567727</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="0"/>
+        <v>8.0157804728024501E-2</v>
+      </c>
+      <c r="K8" t="s">
+        <v>227</v>
+      </c>
+      <c r="L8">
+        <v>0.139873266220092</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="O8" s="8">
+        <v>0.139873266220092</v>
+      </c>
+      <c r="P8" s="1">
+        <f t="shared" si="1"/>
+        <v>7.5881337929074102E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9">
+        <v>5.2704039961099597E-2</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.3540768995881069</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="0"/>
+        <v>7.081538012866781E-2</v>
+      </c>
+      <c r="K9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9">
+        <v>0.13896705210208801</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" s="8">
+        <v>0.53977576106882752</v>
+      </c>
+      <c r="P9" s="1">
+        <f t="shared" si="1"/>
+        <v>0.29282870157001706</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10">
+        <v>5.11732250452041E-2</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.34475790709257037</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="0"/>
+        <v>6.8951581624005942E-2</v>
+      </c>
+      <c r="K10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10">
+        <v>0.13720260560512501</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="O10" s="8">
+        <v>7.5250585496401012E-2</v>
+      </c>
+      <c r="P10" s="1">
+        <f t="shared" si="1"/>
+        <v>4.0823491591510878E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11">
+        <v>4.7353256493806797E-2</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.30373900383710778</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="0"/>
+        <v>6.0747800948464242E-2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11">
+        <v>0.12694919109344399</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="O11" s="8">
+        <v>4.0892086585803955E-2</v>
+      </c>
+      <c r="P11" s="1">
+        <f t="shared" si="1"/>
+        <v>2.2183983578104416E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12">
+        <v>0.68621671199798495</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.269672431051731</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="0"/>
+        <v>5.3934486371083612E-2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12">
+        <v>0.274377854413272</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O12" s="8">
+        <v>0.14040680229663799</v>
+      </c>
+      <c r="P12" s="1">
+        <f t="shared" si="1"/>
+        <v>7.6170781597730802E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13">
+        <v>5.6065507233142797E-2</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.24078582227229983</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="0"/>
+        <v>4.8157164597979606E-2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13">
+        <v>1.3039425855158901E-2</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13" s="8">
+        <v>0.15384382535665703</v>
+      </c>
+      <c r="P13" s="1">
+        <f t="shared" si="1"/>
+        <v>8.346037535021876E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14">
+        <v>5.3621955215930897E-2</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.24012398719787578</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="0"/>
+        <v>4.8024797582700306E-2</v>
+      </c>
+      <c r="K14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L14">
+        <v>1.30021437226209E-2</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="8">
+        <v>0.17386837329132693</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="1"/>
+        <v>9.4323705633195754E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15">
+        <v>5.2865281701087903E-2</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="G15">
+        <v>0.23809316009283019</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>4.761863216048072E-2</v>
+      </c>
+      <c r="K15" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15">
+        <v>1.2918258924410401E-2</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O15" s="8">
+        <v>0.18215205683083158</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="1"/>
+        <v>9.8817609342926743E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16">
+        <v>5.2704039961099597E-2</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16">
+        <v>0.136847808957099</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>2.7369561872987509E-2</v>
+      </c>
+      <c r="K16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16">
+        <v>1.2843694659334499E-2</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" s="8">
+        <v>8.0651906924130184E-2</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="1"/>
+        <v>4.3753711980274432E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17">
+        <v>5.11732250452041E-2</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17">
+        <v>0.13417842984199499</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>2.6835686048375631E-2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>228</v>
+      </c>
+      <c r="L17">
+        <v>1.07558952372075E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18">
+        <v>4.7353256493806797E-2</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="G18">
+        <v>0.1023464500904082</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>2.046929007908492E-2</v>
+      </c>
+      <c r="K18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18">
+        <v>8.1741075589523999E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>0.16493113338947199</v>
+      </c>
+      <c r="K19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L19">
+        <v>5.2356980930791204E-3</v>
+      </c>
+      <c r="O19">
+        <f>SUM(O6:O16)</f>
+        <v>1.8433157616544771</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20">
+        <v>0.15555378794670099</v>
+      </c>
+      <c r="K20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20">
+        <v>4.9523269769302797E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21">
+        <v>0.14743372797966001</v>
+      </c>
+      <c r="G21">
+        <f>SUM(G6:G18)</f>
+        <v>4.9999999850988281</v>
+      </c>
+      <c r="K21" t="s">
+        <v>39</v>
+      </c>
+      <c r="L21">
+        <v>4.2989065208694803E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22">
+        <v>0.14161115884780801</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22">
+        <v>3.8121749566609399E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23">
+        <v>0.136847808957099</v>
+      </c>
+      <c r="K23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23">
+        <v>3.46712895052677E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24">
+        <v>0.13288007676601399</v>
+      </c>
+      <c r="K24" t="s">
+        <v>37</v>
+      </c>
+      <c r="L24">
+        <v>3.3887851713562101E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25">
+        <v>0.120742350816726</v>
+      </c>
+      <c r="K25" t="s">
+        <v>228</v>
+      </c>
+      <c r="L25">
+        <v>2.76870249366586E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26">
+        <v>0.15691475570201799</v>
+      </c>
+      <c r="K26" t="s">
+        <v>38</v>
+      </c>
+      <c r="L26">
+        <v>5.4344338685774199E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27">
+        <v>0.15644374489784199</v>
+      </c>
+      <c r="K27" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27">
+        <v>4.15718148900736E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28">
+        <v>0.15058366954326599</v>
+      </c>
+      <c r="K28" t="s">
+        <v>36</v>
+      </c>
+      <c r="L28">
+        <v>3.1274349533252799E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29">
+        <v>0.13505525887012401</v>
+      </c>
+      <c r="K29" t="s">
+        <v>228</v>
+      </c>
+      <c r="L29">
+        <v>2.4078346294287502E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30">
+        <v>0.13417842984199499</v>
+      </c>
+      <c r="K30" t="s">
+        <v>37</v>
+      </c>
+      <c r="L30">
+        <v>1.30016958733748E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31">
+        <v>0.13413907587528201</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31">
+        <v>7.9140757490105899E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>227</v>
+      </c>
+      <c r="C32">
+        <v>0.13268508017063099</v>
+      </c>
+      <c r="K32" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32">
+        <v>0.13318008906196399</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33">
+        <v>0.44884106516838002</v>
+      </c>
+      <c r="K33" t="s">
+        <v>38</v>
+      </c>
+      <c r="L33">
+        <v>0.115760722591811</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>0.115297175943851</v>
+      </c>
+      <c r="K34" t="s">
+        <v>37</v>
+      </c>
+      <c r="L34">
+        <v>6.3044693241026101E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35">
+        <v>0.11411864310503</v>
+      </c>
+      <c r="K35" t="s">
+        <v>228</v>
+      </c>
+      <c r="L35">
+        <v>5.9318153136098901E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36">
+        <v>8.8290140032768194E-2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>39</v>
+      </c>
+      <c r="L36">
+        <v>3.7901815493897199E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37">
+        <v>7.9414144158363301E-2</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37">
+        <v>2.38880775956875E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38">
+        <v>7.8326664865016896E-2</v>
+      </c>
+      <c r="K38" t="s">
+        <v>36</v>
+      </c>
+      <c r="L38">
+        <v>1.9968629996213901E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39">
+        <v>7.5712136924266801E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F6:G18">
+    <sortCondition descending="1" ref="G6:G18"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224462D2-154F-E14E-902D-7BB3C4C20791}">
+  <dimension ref="C1:O58"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="3:14" x14ac:dyDescent="0.2">
       <c r="L1" t="s">
         <v>41</v>
       </c>
@@ -1179,313 +3076,207 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C2" s="4" t="s">
+    <row r="2" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2">
         <v>7.4550300836563096E-2</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4" t="s">
+      <c r="G2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2">
         <v>182</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="L2" t="s">
         <v>8</v>
       </c>
       <c r="M2">
         <v>5.7726363758063099</v>
       </c>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-    </row>
-    <row r="3" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C3" s="4" t="s">
+    </row>
+    <row r="3" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3">
         <v>5.53501918911933E-2</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
+      <c r="G3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3">
         <v>172</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
       <c r="L3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="M3">
         <v>5.5893528171436397</v>
       </c>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-    </row>
-    <row r="4" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C4" s="4" t="s">
+    </row>
+    <row r="4" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4">
         <v>5.4937630891799899E-2</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
+      <c r="G4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4">
         <v>166</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4" t="s">
+      <c r="L4" t="s">
         <v>12</v>
       </c>
       <c r="M4">
         <v>5.4350027152064104</v>
       </c>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-    </row>
-    <row r="5" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C5" s="4" t="s">
+    </row>
+    <row r="5" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5">
         <v>5.2264954894781099E-2</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
       <c r="G5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5">
         <v>163</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4" t="s">
+      <c r="L5" t="s">
         <v>29</v>
       </c>
       <c r="M5">
         <v>5.40543461493791</v>
       </c>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-    </row>
-    <row r="6" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C6" s="4" t="s">
+    </row>
+    <row r="6" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6">
         <v>5.0640668720006901E-2</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
+      <c r="G6" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6">
         <v>161</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4" t="s">
+      <c r="L6" t="s">
         <v>15</v>
       </c>
       <c r="M6">
         <v>5.3937381248747798</v>
       </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-    </row>
-    <row r="7" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C7" s="4" t="s">
+    </row>
+    <row r="7" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7">
         <v>4.9985952675342497E-2</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
+      <c r="G7" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7">
         <v>158</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4" t="s">
+      <c r="L7" t="s">
         <v>30</v>
       </c>
       <c r="M7">
         <v>5.3823659671146196</v>
       </c>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-    </row>
-    <row r="8" spans="3:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8">
         <v>4.94795329868793E-2</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="G8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8">
         <v>157</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4" t="s">
+      <c r="L8" t="s">
         <v>16</v>
       </c>
       <c r="M8">
         <v>5.3564566263716502</v>
       </c>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-    </row>
-    <row r="9" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C9" s="4" t="s">
+    </row>
+    <row r="9" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9">
         <v>4.9431469291448503E-2</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
+      <c r="G9" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9">
         <v>157</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4" t="s">
+      <c r="L9" t="s">
         <v>20</v>
       </c>
       <c r="M9">
         <v>5.3418608716949896</v>
       </c>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-    </row>
-    <row r="10" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C10" s="4" t="s">
+    </row>
+    <row r="10" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10">
         <v>4.8337239772081299E-2</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="G10" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10">
         <v>157</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4" t="s">
+      <c r="L10" t="s">
         <v>18</v>
       </c>
       <c r="M10">
         <v>5.2663018442704299</v>
       </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-    </row>
-    <row r="11" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C11" s="4" t="s">
+    </row>
+    <row r="11" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11">
         <v>4.8165015876293099E-2</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4" t="s">
+      <c r="G11" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11">
         <v>150</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4" t="s">
+      <c r="L11" t="s">
         <v>19</v>
       </c>
       <c r="M11">
         <v>5.1131044369434697</v>
       </c>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-    </row>
-    <row r="12" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-    </row>
-    <row r="14" spans="3:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C14" t="s">
         <v>46</v>
       </c>
@@ -1505,14 +3296,14 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C15" s="4" t="s">
+    <row r="15" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15">
         <v>6.1020885215345797E-3</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15">
         <v>8.3916349269678395E-4</v>
       </c>
       <c r="H15" t="s">
@@ -1534,14 +3325,14 @@
         <v>8.5595217083204501E-4</v>
       </c>
     </row>
-    <row r="16" spans="3:19" x14ac:dyDescent="0.2">
-      <c r="C16" s="4" t="s">
+    <row r="16" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16">
         <v>5.7277741280002898E-3</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16">
         <v>1.3141233086804099E-3</v>
       </c>
       <c r="H16" t="s">
@@ -1564,13 +3355,13 @@
       </c>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C17" s="4" t="s">
+      <c r="C17" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17">
         <v>5.2358180679266501E-3</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17">
         <v>6.0729591641569798E-4</v>
       </c>
       <c r="H17" t="s">
@@ -1593,13 +3384,13 @@
       </c>
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C18" s="4" t="s">
+      <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18">
         <v>4.4474661207278901E-3</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18">
         <v>8.6457121608789298E-4</v>
       </c>
       <c r="H18" t="s">
@@ -1625,10 +3416,10 @@
       <c r="C19" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19">
         <v>4.2946847356118501E-3</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19">
         <v>6.5938753729910104E-4</v>
       </c>
       <c r="H19" s="3" t="s">
@@ -1654,10 +3445,10 @@
       <c r="C20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20">
         <v>3.5200831130735399E-3</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20">
         <v>5.9389329690648005E-4</v>
       </c>
       <c r="H20" t="s">
@@ -1680,13 +3471,13 @@
       </c>
     </row>
     <row r="21" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C21" s="4" t="s">
+      <c r="C21" t="s">
         <v>1</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21">
         <v>3.50786060226425E-3</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21">
         <v>7.9979851234402604E-4</v>
       </c>
       <c r="H21" t="s">
@@ -1712,10 +3503,10 @@
       <c r="C22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22">
         <v>3.1396574641346102E-3</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22">
         <v>5.4344877734655505E-4</v>
       </c>
       <c r="H22" s="3" t="s">
@@ -1738,13 +3529,13 @@
       </c>
     </row>
     <row r="23" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C23" s="4" t="s">
+      <c r="C23" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23">
         <v>3.1197958840695401E-3</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23">
         <v>8.0574764585319004E-4</v>
       </c>
       <c r="H23" t="s">
@@ -1767,13 +3558,13 @@
       </c>
     </row>
     <row r="24" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C24" s="4" t="s">
+      <c r="C24" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24">
         <v>2.5376988067774301E-3</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24">
         <v>7.0154610188608696E-4</v>
       </c>
       <c r="H24" s="3" t="s">
@@ -1794,11 +3585,6 @@
       <c r="N24">
         <v>1.2792182012327201E-3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
     </row>
     <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" t="s">
@@ -1943,7 +3729,7 @@
         <v>43614</v>
       </c>
     </row>
-    <row r="34" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C34" s="3" t="s">
         <v>6</v>
       </c>
@@ -1981,7 +3767,7 @@
         <v>43614</v>
       </c>
     </row>
-    <row r="35" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C35" s="3" t="s">
         <v>25</v>
       </c>
@@ -2019,7 +3805,7 @@
         <v>43614</v>
       </c>
     </row>
-    <row r="36" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C36" s="3" t="s">
         <v>14</v>
       </c>
@@ -2057,7 +3843,7 @@
         <v>43614</v>
       </c>
     </row>
-    <row r="37" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C37" s="3" t="s">
         <v>21</v>
       </c>
@@ -2095,44 +3881,18 @@
         <v>43614</v>
       </c>
     </row>
-    <row r="40" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C40" s="6" t="s">
+    <row r="40" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C40" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7"/>
-      <c r="P40" s="7"/>
-    </row>
-    <row r="41" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C41" s="6" t="s">
+    </row>
+    <row r="41" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C41" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-      <c r="N41" s="7"/>
-      <c r="O41" s="7"/>
-      <c r="P41" s="7"/>
-    </row>
-    <row r="42" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C42" s="5"/>
+    </row>
+    <row r="42" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C42" s="4"/>
       <c r="E42" t="s">
         <v>55</v>
       </c>
@@ -2167,8 +3927,8 @@
         <v>43614</v>
       </c>
     </row>
-    <row r="43" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C43" s="5"/>
+    <row r="43" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C43" s="4"/>
       <c r="E43" t="s">
         <v>55</v>
       </c>
@@ -2203,8 +3963,8 @@
         <v>43614</v>
       </c>
     </row>
-    <row r="44" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C44" s="5"/>
+    <row r="44" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C44" s="4"/>
       <c r="E44" t="s">
         <v>55</v>
       </c>
@@ -2239,8 +3999,8 @@
         <v>43614</v>
       </c>
     </row>
-    <row r="45" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C45" s="5"/>
+    <row r="45" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C45" s="4"/>
       <c r="E45" t="s">
         <v>55</v>
       </c>
@@ -2275,47 +4035,47 @@
         <v>43614</v>
       </c>
     </row>
-    <row r="46" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C46" s="5"/>
-    </row>
-    <row r="47" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C47" s="5"/>
-    </row>
-    <row r="48" spans="3:16" x14ac:dyDescent="0.2">
-      <c r="C48" s="6" t="s">
+    <row r="46" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C46" s="4"/>
+    </row>
+    <row r="47" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C48" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="49" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="50" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="51" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="52" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="53" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="54" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C54" s="5"/>
+      <c r="C54" s="4"/>
     </row>
     <row r="55" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C55" s="5"/>
+      <c r="C55" s="4"/>
       <c r="E55" t="s">
         <v>55</v>
       </c>
@@ -2351,7 +4111,7 @@
       </c>
     </row>
     <row r="56" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C56" s="5"/>
+      <c r="C56" s="4"/>
       <c r="E56" t="s">
         <v>55</v>
       </c>
@@ -2387,7 +4147,7 @@
       </c>
     </row>
     <row r="57" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C57" s="5"/>
+      <c r="C57" s="4"/>
       <c r="E57" t="s">
         <v>55</v>
       </c>
@@ -2423,7 +4183,6 @@
       </c>
     </row>
     <row r="58" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C58" s="4"/>
       <c r="E58" t="s">
         <v>55</v>
       </c>
@@ -2457,9 +4216,6 @@
       <c r="O58">
         <v>43614</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
-      <c r="C59" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2467,7 +4223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8169409F-4E1C-514B-B309-6A0300B617FB}">
   <dimension ref="B3:O166"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -6340,548 +8096,498 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:E81">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B87:F116">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H167:H1048576 H1:H86 G87:H166 J1:J86 J167:J1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I87:K116">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:J81">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H167:H1048576 H1:H86 G87:H166 J1:J86 J167:J1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B87:F116">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I87:K116">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{784C994C-373B-D24C-86AC-802B504DB4E9}">
-  <dimension ref="A2:N31"/>
+  <dimension ref="B3:R31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4" t="s">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
+      <c r="F3" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
+      <c r="J3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="4"/>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4">
         <v>15.3916479056012</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
+      <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4">
         <v>448</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
+      <c r="J4" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4">
         <v>0.16493113338947199</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="4"/>
+      <c r="P4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5">
         <v>15.2441036308206</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
       <c r="F5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5">
         <v>447</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
       <c r="J5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5">
         <v>0.15555378794670099</v>
       </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4" t="s">
+      <c r="P5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>14.393798779965101</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
       <c r="F6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6">
         <v>434</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
       <c r="J6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6">
         <v>0.14743372797966001</v>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4" t="s">
+      <c r="P6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7">
         <v>14.2139449345147</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4" t="s">
+      <c r="F7" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7">
         <v>426</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
       <c r="J7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7">
         <v>0.14161115884780801</v>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
+      <c r="P7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8">
         <v>13.890312462693601</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
       <c r="F8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8">
         <v>422</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
       <c r="J8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8">
         <v>0.136847808957099</v>
       </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="4"/>
+      <c r="R8" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9">
         <v>13.5857334233093</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4" t="s">
+      <c r="F9" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9">
         <v>414</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4" t="s">
+      <c r="J9" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9">
         <v>0.13288007676601399</v>
       </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4" t="s">
+      <c r="P9" t="s">
+        <v>23</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10">
         <v>13.2804588630952</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
       <c r="F10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10">
         <v>409</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4" t="s">
+      <c r="J10" t="s">
         <v>39</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10">
         <v>0.120742350816726</v>
       </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13">
         <v>5.2590345379383502E-3</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13">
         <v>1.1267786881868299E-3</v>
       </c>
-      <c r="E13" s="4"/>
       <c r="F13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13">
         <v>2.3636484864648401E-3</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13">
         <v>1.15472940296476E-3</v>
       </c>
-      <c r="I13" s="4"/>
       <c r="J13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13">
         <v>5.2356980930791204E-3</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L13">
         <v>1.4300012603516701E-3</v>
       </c>
-      <c r="M13" s="4"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="4"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14">
         <v>5.2573676490198498E-3</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14">
         <v>1.2295088368432601E-3</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14">
         <v>1.9235898119749099E-3</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14">
         <v>1.01324911123461E-3</v>
       </c>
-      <c r="I14" s="4"/>
       <c r="J14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14">
         <v>4.9523269769302797E-3</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14">
         <v>1.75953449691788E-3</v>
       </c>
-      <c r="M14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15">
         <v>4.6972929723963002E-3</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15">
         <v>1.39672560375464E-3</v>
       </c>
-      <c r="E15" s="4"/>
       <c r="F15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15">
         <v>1.9052540338711601E-3</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15">
         <v>1.14380771020209E-3</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15">
         <v>4.2989065208694803E-3</v>
       </c>
-      <c r="L15" s="4">
+      <c r="L15">
         <v>1.0255485811918701E-3</v>
       </c>
-      <c r="M15" s="4"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="4"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16">
         <v>4.28390452060273E-3</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16">
         <v>7.2097522298963902E-4</v>
       </c>
-      <c r="E16" s="4"/>
       <c r="F16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16">
         <v>1.2751700226696599E-3</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16">
         <v>9.4799681969324296E-4</v>
       </c>
-      <c r="I16" s="4"/>
       <c r="J16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16">
         <v>3.8121749566609399E-3</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L16">
         <v>7.1746159946730996E-4</v>
       </c>
-      <c r="M16" s="4"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="4"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17">
         <v>2.7570342712361301E-3</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17">
         <v>1.07016864937833E-3</v>
       </c>
-      <c r="E17" s="4"/>
       <c r="F17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17">
         <v>9.0512068275767595E-4</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17">
         <v>6.0073020812069901E-4</v>
       </c>
-      <c r="I17" s="4"/>
       <c r="J17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17">
         <v>3.46712895052677E-3</v>
       </c>
-      <c r="L17" s="4">
+      <c r="L17">
         <v>1.0069995891738501E-3</v>
       </c>
-      <c r="M17" s="4"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4" t="s">
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18">
         <v>2.25196692892383E-3</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18">
         <v>1.13344646869634E-3</v>
       </c>
-      <c r="E18" s="4"/>
       <c r="F18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18">
         <v>3.3004400586742399E-4</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18">
         <v>9.0666499803019902E-4</v>
       </c>
-      <c r="I18" s="4"/>
       <c r="J18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18">
         <v>3.3887851713562101E-3</v>
       </c>
-      <c r="L18" s="4">
+      <c r="L18">
         <v>1.0024933816547199E-3</v>
       </c>
-      <c r="M18" s="4"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="4"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19">
         <v>1.85191358847842E-3</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19">
         <v>1.2447419755071099E-3</v>
       </c>
-      <c r="E19" s="4"/>
       <c r="F19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19">
         <v>-1.0884784637951799E-3</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19">
         <v>7.9060631023153904E-4</v>
       </c>
-      <c r="I19" s="4"/>
       <c r="J19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19">
         <v>2.76870249366586E-3</v>
       </c>
-      <c r="L19" s="4">
+      <c r="L19">
         <v>7.9426688509214396E-4</v>
       </c>
-      <c r="M19" s="4"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4" t="s">
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
         <v>62</v>
       </c>
       <c r="D22" t="s">
@@ -6918,8 +8624,7 @@
         <v>39974</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="4"/>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
       <c r="D23" t="s">
         <v>55</v>
       </c>
@@ -6954,7 +8659,7 @@
         <v>39974</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
       <c r="D24" t="s">
         <v>55</v>
       </c>
@@ -6989,7 +8694,7 @@
         <v>39974</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
       <c r="D25" t="s">
         <v>55</v>
       </c>
@@ -7024,41 +8729,40 @@
         <v>39974</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B28" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="4"/>
       <c r="D28" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" t="s">
         <v>57</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28">
         <v>0.51719999999999999</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" t="s">
         <v>56</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" t="s">
         <v>58</v>
       </c>
-      <c r="J28" s="4">
+      <c r="J28">
         <v>0.52370000000000005</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="K28" t="s">
         <v>59</v>
       </c>
-      <c r="L28" s="4">
+      <c r="L28">
         <v>0.65100000000000002</v>
       </c>
       <c r="M28" t="s">
@@ -7068,21 +8772,20 @@
         <v>39974</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="4"/>
       <c r="D29" t="s">
         <v>55</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" t="s">
         <v>56</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" t="s">
         <v>57</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29">
         <v>0.5111</v>
       </c>
       <c r="H29" t="s">
@@ -7107,20 +8810,20 @@
         <v>39974</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D30" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" t="s">
         <v>57</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30">
         <v>0.51139999999999997</v>
       </c>
       <c r="H30" t="s">
@@ -7145,7 +8848,7 @@
         <v>39974</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>36</v>
       </c>
@@ -7189,7 +8892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F58ED9CA-9E2C-AF43-A121-F1B5E3CDAC29}">
   <dimension ref="B3:O42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -7774,7 +9477,7 @@
       </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B32" s="4" t="s">
+      <c r="B32" t="s">
         <v>62</v>
       </c>
       <c r="E32" t="s">
